--- a/results/trace_evochart_temp06_seed42_qwen25vl7b_base_vs_answer_20260715T000059Z_results.xlsx
+++ b/results/trace_evochart_temp06_seed42_qwen25vl7b_base_vs_answer_20260715T000059Z_results.xlsx
@@ -152,7 +152,7 @@
     <t>trace_evochart_temp06_seed42</t>
   </si>
   <si>
-    <t>/home/shadeform/trace/benchmark/subsets/trace_candidate37_200</t>
+    <t>full EvoChart dataset (1,250 rows; no sampled subset)</t>
   </si>
   <si>
     <t>qwen25vl7b-base, trace-qwen25vl7b-easyr1-all1000-answer-nokl-step500</t>
